--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N7_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6491254249842</v>
+        <v>1.892982881559933</v>
       </c>
       <c r="D2" t="n">
-        <v>11.80850430198033</v>
+        <v>1.918881949071804</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
